--- a/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
+++ b/tests/eindhoven-500/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Auto_Fiets.xlsx
@@ -436,7 +436,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>35.78905222296921</v>
+        <v>35.7890522229692</v>
       </c>
       <c r="C5">
         <v>35.43554381847746</v>
@@ -2340,7 +2340,7 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>73.05323894430344</v>
+        <v>73.05323894430343</v>
       </c>
       <c r="C117">
         <v>60.74065703252848</v>
@@ -3190,7 +3190,7 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>2.303233722300744</v>
+        <v>2.303233722300743</v>
       </c>
       <c r="C167">
         <v>2.384001759053796</v>
@@ -5094,7 +5094,7 @@
         <v>278</v>
       </c>
       <c r="B279">
-        <v>61.21218399447125</v>
+        <v>61.21218399447124</v>
       </c>
       <c r="C279">
         <v>67.79711037697518</v>
@@ -6709,7 +6709,7 @@
         <v>373</v>
       </c>
       <c r="B374">
-        <v>566.67079611286</v>
+        <v>566.6707961128599</v>
       </c>
       <c r="C374">
         <v>661.4910760738777</v>
@@ -7372,7 +7372,7 @@
         <v>412</v>
       </c>
       <c r="B413">
-        <v>21.60468417606317</v>
+        <v>21.60468417606316</v>
       </c>
       <c r="C413">
         <v>15.80714377541785</v>
